--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260902.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260902.xlsx
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>12,847,134</t>
+          <t>855,349</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>855,349</t>
+          <t>12,847,134</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>202609WTEU6F</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,828,000</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>202609WTEU6F</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1,828,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>10,576,121</t>
+          <t>7,152,249</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>7,152,249</t>
+          <t>10,576,121</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>581,000</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>581,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202609WVHFU6F</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>202609WVHFU6F</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2,185,107</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>2,185,107</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>4,948,956</t>
+          <t>774,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>774,000</t>
+          <t>290,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>290,000</t>
+          <t>227,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>227,000</t>
+          <t>4,948,956</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,001,121</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>1,001,121</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>156,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>330,000</t>
+          <t>156,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>330,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>253,000</t>
+          <t>678,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>678,000</t>
+          <t>253,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>335,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2207,17 +2207,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>335,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
